--- a/artfynd/A 16997-2026 artfynd.xlsx
+++ b/artfynd/A 16997-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131623861</v>
       </c>
       <c r="B3" t="n">
-        <v>92477</v>
+        <v>92480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16997-2026 artfynd.xlsx
+++ b/artfynd/A 16997-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131623861</v>
       </c>
       <c r="B3" t="n">
-        <v>92480</v>
+        <v>92486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16997-2026 artfynd.xlsx
+++ b/artfynd/A 16997-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131623861</v>
       </c>
       <c r="B3" t="n">
-        <v>92486</v>
+        <v>92496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16997-2026 artfynd.xlsx
+++ b/artfynd/A 16997-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131623861</v>
       </c>
       <c r="B3" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16997-2026 artfynd.xlsx
+++ b/artfynd/A 16997-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131623861</v>
       </c>
       <c r="B3" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16997-2026 artfynd.xlsx
+++ b/artfynd/A 16997-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131623861</v>
       </c>
       <c r="B3" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16997-2026 artfynd.xlsx
+++ b/artfynd/A 16997-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110985676</v>
+        <v>131623953</v>
       </c>
       <c r="B2" t="n">
-        <v>103838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vändburgs Lövskog Långmyre 1:20, Vändburg, Gtl</t>
+          <t>Hamra Långmyre 1:20, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700930.2337680594</v>
+        <v>700924</v>
       </c>
       <c r="R2" t="n">
-        <v>6316007.372153432</v>
+        <v>6316041</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal platsar inom ramen skyddsvärda träd.</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Arvid Svanborg</t>
+          <t>Johan Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Arvid Svanborg</t>
+          <t>Johan Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131623861</v>
+        <v>131623855</v>
       </c>
       <c r="B3" t="n">
-        <v>92500</v>
+        <v>92534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,7 +822,7 @@
         <v>701001</v>
       </c>
       <c r="R3" t="n">
-        <v>6316022</v>
+        <v>6316028</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,6 +879,323 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131623861</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92534</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hamra Långmyre 1:20, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>701001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6316022</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hamra</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131623930</v>
+      </c>
+      <c r="B5" t="n">
+        <v>81701</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3929</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Läderskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Encoelia furfuracea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Roth.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hamra Långmyre 1:20, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>700942</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6316051</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hamra</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110985676</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vändburgs Lövskog Långmyre 1:20, Vändburg, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>700930</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6316007</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hamra</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal platsar inom ramen skyddsvärda träd.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Arvid Svanborg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Arvid Svanborg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16997-2026 artfynd.xlsx
+++ b/artfynd/A 16997-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131623953</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131623855</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131623861</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131623930</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,8 +1221,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110985676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>